--- a/Data/KW_dunn_results_withing_month.xlsx
+++ b/Data/KW_dunn_results_withing_month.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yaroslav\OneDrive\Рабочий стол\Python_repos\Python_projects_ICG_SB_RAS\Four_host_species_OF\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53B09FA-119E-4826-B10A-22B27B3F1687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liver_results" sheetId="1" r:id="rId1"/>
     <sheet name="Fluke_results" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -113,8 +119,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,7 +168,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -185,11 +191,106 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -198,19 +299,46 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -248,7 +376,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -282,6 +410,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -316,9 +445,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -491,11 +621,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q58"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R58"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -506,7 +636,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -517,7 +647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -528,7 +658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -566,7 +696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -577,7 +707,7 @@
         <v>0.06</v>
       </c>
       <c r="D5" s="4">
-        <v>0.598</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="E5" s="4">
         <v>0.85</v>
@@ -589,13 +719,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="J5" s="4">
         <v>0.314</v>
       </c>
       <c r="K5" s="4">
-        <v>0.119</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>0</v>
@@ -604,16 +734,16 @@
         <v>1</v>
       </c>
       <c r="O5" s="4">
-        <v>0.708</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="P5" s="4">
         <v>0.372</v>
       </c>
       <c r="Q5" s="5">
-        <v>0.042</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>4.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -624,7 +754,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="E6" s="4">
         <v>0.06</v>
@@ -633,22 +763,22 @@
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
       </c>
       <c r="J6" s="4">
-        <v>0.259</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="K6" s="4">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.708</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="O6" s="4">
         <v>1</v>
@@ -657,24 +787,24 @@
         <v>0.247</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.074</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
+        <v>7.3999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="4">
-        <v>0.598</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="C7" s="4">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>0.579</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
@@ -683,13 +813,13 @@
         <v>0.314</v>
       </c>
       <c r="I7" s="4">
-        <v>0.259</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="J7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>0.008999999999999999</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>2</v>
@@ -704,10 +834,10 @@
         <v>1</v>
       </c>
       <c r="Q7" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -718,7 +848,7 @@
         <v>0.06</v>
       </c>
       <c r="D8" s="4">
-        <v>0.579</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -727,13 +857,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>0.119</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="I8" s="4">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="J8" s="5">
-        <v>0.008999999999999999</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -742,19 +872,19 @@
         <v>3</v>
       </c>
       <c r="N8" s="5">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>0.074</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="P8" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -765,7 +895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -776,7 +906,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -787,7 +917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>0</v>
       </c>
@@ -825,7 +955,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -833,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="4">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="D15" s="4">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="E15" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>0</v>
@@ -848,13 +978,13 @@
         <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="J15" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="K15" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>0</v>
@@ -863,121 +993,121 @@
         <v>1</v>
       </c>
       <c r="O15" s="4">
-        <v>0.574</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="P15" s="4">
-        <v>0.328</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.056</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B16" s="4">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="4">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="E16" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H16" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
       </c>
       <c r="J16" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="K16" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>0.574</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="O16" s="4">
         <v>1</v>
       </c>
       <c r="P16" s="4">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+        <v>0.14599999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="4">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="C17" s="4">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="I17" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N17" s="4">
-        <v>0.328</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="O17" s="4">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="P17" s="4">
         <v>1</v>
       </c>
       <c r="Q17" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="C18" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="D18" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -986,13 +1116,13 @@
         <v>3</v>
       </c>
       <c r="H18" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I18" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="J18" s="5">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
@@ -1001,52 +1131,99 @@
         <v>3</v>
       </c>
       <c r="N18" s="4">
-        <v>0.056</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="O18" s="4">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="P18" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
-      <c r="A21" s="1" t="s">
+    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
-      <c r="A22" s="2" t="s">
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="9"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="A23" s="1" t="s">
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="13"/>
+    </row>
+    <row r="23" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="13"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="16"/>
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1059,6 +1236,8 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
       <c r="H24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1071,6 +1250,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
       <c r="N24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1083,229 +1264,328 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="4">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4">
-        <v>0.778</v>
-      </c>
-      <c r="D25" s="4">
+      <c r="R24" s="13"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="18">
+        <v>1</v>
+      </c>
+      <c r="C25" s="18">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="D25" s="18">
         <v>0.749</v>
       </c>
-      <c r="E25" s="4">
-        <v>0.677</v>
-      </c>
+      <c r="E25" s="18">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="F25" s="11"/>
       <c r="G25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H25" s="4">
-        <v>1</v>
-      </c>
-      <c r="I25" s="4">
-        <v>1</v>
-      </c>
-      <c r="J25" s="5">
-        <v>0.054</v>
-      </c>
-      <c r="K25" s="5">
-        <v>0.054</v>
-      </c>
+      <c r="H25" s="18">
+        <v>1</v>
+      </c>
+      <c r="I25" s="18">
+        <v>1</v>
+      </c>
+      <c r="J25" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="K25" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L25" s="11"/>
       <c r="M25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N25" s="4">
-        <v>1</v>
-      </c>
-      <c r="O25" s="4">
-        <v>0.285</v>
-      </c>
-      <c r="P25" s="5">
-        <v>0.022</v>
-      </c>
-      <c r="Q25" s="4">
+      <c r="N25" s="18">
+        <v>1</v>
+      </c>
+      <c r="O25" s="18">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="P25" s="19">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q25" s="18">
         <v>0.17</v>
       </c>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="4">
-        <v>0.778</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0.677</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0.677</v>
-      </c>
+      <c r="R25" s="13"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="18">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="C26" s="18">
+        <v>1</v>
+      </c>
+      <c r="D26" s="18">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="E26" s="18">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="F26" s="11"/>
       <c r="G26" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H26" s="4">
-        <v>1</v>
-      </c>
-      <c r="I26" s="4">
-        <v>1</v>
-      </c>
-      <c r="J26" s="5">
-        <v>0.054</v>
-      </c>
-      <c r="K26" s="5">
-        <v>0.054</v>
-      </c>
+      <c r="H26" s="18">
+        <v>1</v>
+      </c>
+      <c r="I26" s="18">
+        <v>1</v>
+      </c>
+      <c r="J26" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="K26" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L26" s="11"/>
       <c r="M26" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="N26" s="4">
-        <v>0.285</v>
-      </c>
-      <c r="O26" s="4">
-        <v>1</v>
-      </c>
-      <c r="P26" s="4">
+      <c r="N26" s="18">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="O26" s="18">
+        <v>1</v>
+      </c>
+      <c r="P26" s="18">
         <v>0.17</v>
       </c>
-      <c r="Q26" s="5">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="4">
+      <c r="Q26" s="19">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="R26" s="13"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="18">
         <v>0.749</v>
       </c>
-      <c r="C27" s="4">
-        <v>0.677</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0.778</v>
-      </c>
+      <c r="C27" s="18">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="D27" s="18">
+        <v>1</v>
+      </c>
+      <c r="E27" s="18">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="F27" s="11"/>
       <c r="G27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H27" s="5">
-        <v>0.054</v>
-      </c>
-      <c r="I27" s="5">
-        <v>0.054</v>
-      </c>
-      <c r="J27" s="4">
-        <v>1</v>
-      </c>
-      <c r="K27" s="5">
-        <v>0</v>
-      </c>
+      <c r="H27" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I27" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J27" s="18">
+        <v>1</v>
+      </c>
+      <c r="K27" s="19">
+        <v>0</v>
+      </c>
+      <c r="L27" s="11"/>
       <c r="M27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="N27" s="5">
-        <v>0.022</v>
-      </c>
-      <c r="O27" s="4">
+      <c r="N27" s="19">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="O27" s="18">
         <v>0.17</v>
       </c>
-      <c r="P27" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="4">
-        <v>0.677</v>
-      </c>
-      <c r="C28" s="4">
-        <v>0.677</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0.778</v>
-      </c>
-      <c r="E28" s="4">
-        <v>1</v>
-      </c>
+      <c r="P27" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>0</v>
+      </c>
+      <c r="R27" s="13"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="18">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="C28" s="18">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="D28" s="18">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="E28" s="18">
+        <v>1</v>
+      </c>
+      <c r="F28" s="11"/>
       <c r="G28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H28" s="5">
-        <v>0.054</v>
-      </c>
-      <c r="I28" s="5">
-        <v>0.054</v>
-      </c>
-      <c r="J28" s="5">
-        <v>0</v>
-      </c>
-      <c r="K28" s="4">
-        <v>1</v>
-      </c>
+      <c r="H28" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I28" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0</v>
+      </c>
+      <c r="K28" s="18">
+        <v>1</v>
+      </c>
+      <c r="L28" s="11"/>
       <c r="M28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N28" s="4">
+      <c r="N28" s="18">
         <v>0.17</v>
       </c>
-      <c r="O28" s="5">
-        <v>0.022</v>
-      </c>
-      <c r="P28" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31" s="1" t="s">
+      <c r="O28" s="19">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="18">
+        <v>1</v>
+      </c>
+      <c r="R28" s="13"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" s="16"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="13"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" s="16"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="13"/>
+    </row>
+    <row r="31" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" s="2" t="s">
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="13"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33" s="1" t="s">
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="13"/>
+    </row>
+    <row r="33" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="13"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="16"/>
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1318,6 +1598,8 @@
       <c r="E34" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
       <c r="H34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1330,6 +1612,8 @@
       <c r="K34" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
       <c r="N34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1342,196 +1626,229 @@
       <c r="Q34" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="A35" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="4">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4">
+      <c r="R34" s="13"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="18">
+        <v>1</v>
+      </c>
+      <c r="C35" s="18">
         <v>0.3</v>
       </c>
-      <c r="D35" s="4">
-        <v>0.238</v>
-      </c>
-      <c r="E35" s="4">
-        <v>0.978</v>
-      </c>
+      <c r="D35" s="18">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="E35" s="18">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="F35" s="11"/>
       <c r="G35" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H35" s="4">
-        <v>1</v>
-      </c>
-      <c r="I35" s="4">
-        <v>0.239</v>
-      </c>
-      <c r="J35" s="4">
+      <c r="H35" s="18">
+        <v>1</v>
+      </c>
+      <c r="I35" s="18">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="J35" s="18">
         <v>0.218</v>
       </c>
-      <c r="K35" s="5">
-        <v>0.024</v>
-      </c>
+      <c r="K35" s="19">
+        <v>2.4E-2</v>
+      </c>
+      <c r="L35" s="11"/>
       <c r="M35" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N35" s="4">
-        <v>1</v>
-      </c>
-      <c r="O35" s="4">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="P35" s="4">
+      <c r="N35" s="18">
+        <v>1</v>
+      </c>
+      <c r="O35" s="18">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="P35" s="18">
         <v>0.223</v>
       </c>
-      <c r="Q35" s="4">
-        <v>0.079</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="A36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="4">
+      <c r="Q35" s="18">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="R35" s="13"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="18">
         <v>0.3</v>
       </c>
-      <c r="C36" s="4">
-        <v>1</v>
-      </c>
-      <c r="D36" s="4">
-        <v>0.763</v>
-      </c>
-      <c r="E36" s="4">
+      <c r="C36" s="18">
+        <v>1</v>
+      </c>
+      <c r="D36" s="18">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="E36" s="18">
         <v>0.3</v>
       </c>
+      <c r="F36" s="11"/>
       <c r="G36" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H36" s="4">
-        <v>0.239</v>
-      </c>
-      <c r="I36" s="4">
-        <v>1</v>
-      </c>
-      <c r="J36" s="5">
-        <v>0.024</v>
-      </c>
-      <c r="K36" s="4">
+      <c r="H36" s="18">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="I36" s="18">
+        <v>1</v>
+      </c>
+      <c r="J36" s="19">
+        <v>2.4E-2</v>
+      </c>
+      <c r="K36" s="18">
         <v>0.218</v>
       </c>
+      <c r="L36" s="11"/>
       <c r="M36" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="N36" s="4">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="O36" s="4">
-        <v>1</v>
-      </c>
-      <c r="P36" s="4">
-        <v>0.356</v>
-      </c>
-      <c r="Q36" s="5">
-        <v>0.041</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" s="4">
-        <v>0.238</v>
-      </c>
-      <c r="C37" s="4">
-        <v>0.763</v>
-      </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4">
-        <v>0.238</v>
-      </c>
+      <c r="N36" s="18">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="O36" s="18">
+        <v>1</v>
+      </c>
+      <c r="P36" s="18">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="Q36" s="19">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="R36" s="13"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="18">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="C37" s="18">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="D37" s="18">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="F37" s="11"/>
       <c r="G37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H37" s="18">
         <v>0.218</v>
       </c>
-      <c r="I37" s="5">
-        <v>0.024</v>
-      </c>
-      <c r="J37" s="4">
-        <v>1</v>
-      </c>
-      <c r="K37" s="5">
-        <v>0</v>
-      </c>
+      <c r="I37" s="19">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J37" s="18">
+        <v>1</v>
+      </c>
+      <c r="K37" s="19">
+        <v>0</v>
+      </c>
+      <c r="L37" s="11"/>
       <c r="M37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="N37" s="4">
+      <c r="N37" s="18">
         <v>0.223</v>
       </c>
-      <c r="O37" s="4">
-        <v>0.356</v>
-      </c>
-      <c r="P37" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="4">
-        <v>0.978</v>
-      </c>
-      <c r="C38" s="4">
+      <c r="O37" s="18">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="P37" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="19">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R37" s="13"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="18">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="C38" s="18">
         <v>0.3</v>
       </c>
-      <c r="D38" s="4">
-        <v>0.238</v>
-      </c>
-      <c r="E38" s="4">
-        <v>1</v>
-      </c>
+      <c r="D38" s="18">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="E38" s="18">
+        <v>1</v>
+      </c>
+      <c r="F38" s="11"/>
       <c r="G38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H38" s="5">
-        <v>0.024</v>
-      </c>
-      <c r="I38" s="4">
+      <c r="H38" s="19">
+        <v>2.4E-2</v>
+      </c>
+      <c r="I38" s="18">
         <v>0.218</v>
       </c>
-      <c r="J38" s="5">
-        <v>0</v>
-      </c>
-      <c r="K38" s="4">
-        <v>1</v>
-      </c>
+      <c r="J38" s="19">
+        <v>0</v>
+      </c>
+      <c r="K38" s="18">
+        <v>1</v>
+      </c>
+      <c r="L38" s="11"/>
       <c r="M38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="4">
-        <v>0.079</v>
-      </c>
-      <c r="O38" s="5">
-        <v>0.041</v>
-      </c>
-      <c r="P38" s="5">
-        <v>0.003</v>
-      </c>
-      <c r="Q38" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="N38" s="18">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="O38" s="19">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="P38" s="19">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>1</v>
+      </c>
+      <c r="R38" s="13"/>
+    </row>
+    <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="20"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="21"/>
+      <c r="P39" s="21"/>
+      <c r="Q39" s="21"/>
+      <c r="R39" s="22"/>
+    </row>
+    <row r="41" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
@@ -1542,7 +1859,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -1553,7 +1870,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1564,7 +1881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>0</v>
       </c>
@@ -1610,13 +1927,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="4">
-        <v>0.788</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="D45" s="5">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="E45" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>0</v>
@@ -1625,13 +1942,13 @@
         <v>1</v>
       </c>
       <c r="I45" s="4">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="J45" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="K45" s="4">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>0</v>
@@ -1640,27 +1957,27 @@
         <v>1</v>
       </c>
       <c r="O45" s="4">
-        <v>0.349</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="P45" s="5">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="Q45" s="4">
-        <v>0.171</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B46" s="4">
-        <v>0.788</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="C46" s="4">
         <v>1</v>
       </c>
       <c r="D46" s="5">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E46" s="4">
         <v>0.221</v>
@@ -1669,22 +1986,22 @@
         <v>1</v>
       </c>
       <c r="H46" s="4">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="I46" s="4">
         <v>1</v>
       </c>
       <c r="J46" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="K46" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N46" s="4">
-        <v>0.349</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
@@ -1693,18 +2010,18 @@
         <v>0.187</v>
       </c>
       <c r="Q46" s="5">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B47" s="5">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="C47" s="5">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="D47" s="4">
         <v>1</v>
@@ -1716,22 +2033,22 @@
         <v>2</v>
       </c>
       <c r="H47" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="I47" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="J47" s="4">
         <v>1</v>
       </c>
       <c r="K47" s="4">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N47" s="5">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="O47" s="4">
         <v>0.187</v>
@@ -1743,12 +2060,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B48" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="C48" s="4">
         <v>0.221</v>
@@ -1763,13 +2080,13 @@
         <v>3</v>
       </c>
       <c r="H48" s="4">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="I48" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="J48" s="4">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="K48" s="4">
         <v>1</v>
@@ -1778,10 +2095,10 @@
         <v>3</v>
       </c>
       <c r="N48" s="4">
-        <v>0.171</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="O48" s="5">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="P48" s="5">
         <v>0</v>
@@ -1790,7 +2107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>4</v>
       </c>
@@ -1801,7 +2118,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>11</v>
       </c>
@@ -1812,7 +2129,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>6</v>
       </c>
@@ -1823,7 +2140,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>0</v>
       </c>
@@ -1861,7 +2178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>0</v>
       </c>
@@ -1869,13 +2186,13 @@
         <v>1</v>
       </c>
       <c r="C55" s="4">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="D55" s="4">
-        <v>0.341</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="E55" s="4">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>0</v>
@@ -1884,13 +2201,13 @@
         <v>1</v>
       </c>
       <c r="I55" s="4">
-        <v>0.274</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="J55" s="4">
         <v>0.19</v>
       </c>
       <c r="K55" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>0</v>
@@ -1902,33 +2219,33 @@
         <v>0.246</v>
       </c>
       <c r="P55" s="4">
-        <v>0.392</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="Q55" s="5">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B56" s="4">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="C56" s="4">
         <v>1</v>
       </c>
       <c r="D56" s="4">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="E56" s="4">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H56" s="4">
-        <v>0.274</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="I56" s="4">
         <v>1</v>
@@ -1937,7 +2254,7 @@
         <v>0.748</v>
       </c>
       <c r="K56" s="5">
-        <v>0.051</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>1</v>
@@ -1949,27 +2266,27 @@
         <v>1</v>
       </c>
       <c r="P56" s="5">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="Q56" s="4">
-        <v>0.392</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17">
+        <v>0.39200000000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B57" s="4">
-        <v>0.341</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="C57" s="4">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="D57" s="4">
         <v>1</v>
       </c>
       <c r="E57" s="4">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>2</v>
@@ -1984,36 +2301,36 @@
         <v>1</v>
       </c>
       <c r="K57" s="4">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N57" s="4">
-        <v>0.392</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="O57" s="5">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="P57" s="4">
         <v>1</v>
       </c>
       <c r="Q57" s="5">
-        <v>0.008</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B58" s="4">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="C58" s="4">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="D58" s="4">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="E58" s="4">
         <v>1</v>
@@ -2022,13 +2339,13 @@
         <v>3</v>
       </c>
       <c r="H58" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="I58" s="5">
-        <v>0.051</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="J58" s="4">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="K58" s="4">
         <v>1</v>
@@ -2037,13 +2354,13 @@
         <v>3</v>
       </c>
       <c r="N58" s="5">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="O58" s="4">
-        <v>0.392</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="P58" s="5">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="Q58" s="4">
         <v>1</v>
@@ -2055,11 +2372,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -2067,7 +2384,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -2075,7 +2392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2083,7 +2400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -2109,7 +2426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -2120,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E5" s="4">
-        <v>0.765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>0</v>
@@ -2135,13 +2452,13 @@
         <v>0.2</v>
       </c>
       <c r="J5" s="5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="K5" s="4">
-        <v>0.266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>0.26600000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -2152,10 +2469,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E6" s="4">
-        <v>0.765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>1</v>
@@ -2170,30 +2487,30 @@
         <v>0.2</v>
       </c>
       <c r="K6" s="5">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="C7" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I7" s="4">
         <v>0.2</v>
@@ -2202,21 +2519,21 @@
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="4">
-        <v>0.765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="C8" s="4">
-        <v>0.765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="D8" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -2225,19 +2542,19 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="I8" s="5">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="J8" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -2245,7 +2562,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2253,7 +2570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -2261,7 +2578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>0</v>
       </c>
@@ -2287,7 +2604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -2298,10 +2615,10 @@
         <v>0.95</v>
       </c>
       <c r="D15" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E15" s="4">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>0</v>
@@ -2313,13 +2630,13 @@
         <v>0.214</v>
       </c>
       <c r="J15" s="4">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="K15" s="4">
         <v>0.15</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
@@ -2330,10 +2647,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E16" s="4">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1</v>
@@ -2345,56 +2662,56 @@
         <v>1</v>
       </c>
       <c r="J16" s="4">
-        <v>0.647</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="K16" s="5">
-        <v>0.008</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="C17" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="4">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="I17" s="4">
-        <v>0.647</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="C18" s="4">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="D18" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -2406,16 +2723,16 @@
         <v>0.15</v>
       </c>
       <c r="I18" s="5">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="J18" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -2423,7 +2740,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
@@ -2431,7 +2748,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -2439,7 +2756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -2465,7 +2782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
@@ -2473,10 +2790,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="4">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="D25" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
@@ -2488,36 +2805,36 @@
         <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="J25" s="5">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="K25" s="4">
-        <v>0.362</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>0.36199999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="E26" s="4">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H26" s="4">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
@@ -2526,30 +2843,30 @@
         <v>0.123</v>
       </c>
       <c r="K26" s="4">
-        <v>0.094</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="C27" s="5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H27" s="5">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I27" s="4">
         <v>0.123</v>
@@ -2558,10 +2875,10 @@
         <v>1</v>
       </c>
       <c r="K27" s="5">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>3</v>
       </c>
@@ -2569,10 +2886,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="4">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="D28" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="E28" s="4">
         <v>1</v>
@@ -2581,19 +2898,19 @@
         <v>3</v>
       </c>
       <c r="H28" s="4">
-        <v>0.362</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="I28" s="4">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="J28" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>12</v>
       </c>
@@ -2601,7 +2918,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
@@ -2609,7 +2926,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -2617,7 +2934,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -2643,7 +2960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>0</v>
       </c>
@@ -2654,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="E35" s="4">
         <v>1</v>
@@ -2666,16 +2983,16 @@
         <v>1</v>
       </c>
       <c r="I35" s="4">
-        <v>0.8149999999999999</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="J35" s="5">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="K35" s="4">
-        <v>0.536</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>0.53600000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>1</v>
       </c>
@@ -2686,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
@@ -2695,51 +3012,51 @@
         <v>1</v>
       </c>
       <c r="H36" s="4">
-        <v>0.8149999999999999</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
       </c>
       <c r="J36" s="5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="K36" s="4">
         <v>0.48</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="C37" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H37" s="5">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="I37" s="5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="J37" s="4">
         <v>1</v>
       </c>
       <c r="K37" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -2759,13 +3076,13 @@
         <v>3</v>
       </c>
       <c r="H38" s="4">
-        <v>0.536</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="I38" s="4">
         <v>0.48</v>
       </c>
       <c r="J38" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="K38" s="4">
         <v>1</v>

--- a/Data/KW_dunn_results_withing_month.xlsx
+++ b/Data/KW_dunn_results_withing_month.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yaroslav\OneDrive\Рабочий стол\Python_repos\Python_projects_ICG_SB_RAS\Four_host_species_OF\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53B09FA-119E-4826-B10A-22B27B3F1687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76438AB-565E-4583-A9F7-FCC85BEBA381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liver_results" sheetId="1" r:id="rId1"/>
@@ -290,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -304,17 +304,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1174,56 +1169,28 @@
       <c r="A22" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="13"/>
+      <c r="R22" s="11"/>
     </row>
     <row r="23" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="15" t="s">
+      <c r="M23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="13"/>
+      <c r="R23" s="11"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
+      <c r="A24" s="13"/>
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1236,8 +1203,6 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
       <c r="H24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1250,8 +1215,6 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
       <c r="N24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1264,328 +1227,246 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="13"/>
+      <c r="R24" s="11"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="18">
-        <v>1</v>
-      </c>
-      <c r="C25" s="18">
+      <c r="A25" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="4">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4">
         <v>0.77800000000000002</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="4">
         <v>0.749</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="4">
         <v>0.67700000000000005</v>
       </c>
-      <c r="F25" s="11"/>
       <c r="G25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H25" s="18">
-        <v>1</v>
-      </c>
-      <c r="I25" s="18">
-        <v>1</v>
-      </c>
-      <c r="J25" s="19">
+      <c r="H25" s="4">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
+      <c r="J25" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="L25" s="11"/>
       <c r="M25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N25" s="18">
-        <v>1</v>
-      </c>
-      <c r="O25" s="18">
+      <c r="N25" s="4">
+        <v>1</v>
+      </c>
+      <c r="O25" s="4">
         <v>0.28499999999999998</v>
       </c>
-      <c r="P25" s="19">
+      <c r="P25" s="5">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="Q25" s="18">
+      <c r="Q25" s="4">
         <v>0.17</v>
       </c>
-      <c r="R25" s="13"/>
+      <c r="R25" s="11"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="18">
+      <c r="A26" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="4">
         <v>0.77800000000000002</v>
       </c>
-      <c r="C26" s="18">
-        <v>1</v>
-      </c>
-      <c r="D26" s="18">
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+      <c r="D26" s="4">
         <v>0.67700000000000005</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="4">
         <v>0.67700000000000005</v>
       </c>
-      <c r="F26" s="11"/>
       <c r="G26" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H26" s="18">
-        <v>1</v>
-      </c>
-      <c r="I26" s="18">
-        <v>1</v>
-      </c>
-      <c r="J26" s="19">
+      <c r="H26" s="4">
+        <v>1</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+      <c r="J26" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="L26" s="11"/>
       <c r="M26" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="N26" s="18">
+      <c r="N26" s="4">
         <v>0.28499999999999998</v>
       </c>
-      <c r="O26" s="18">
-        <v>1</v>
-      </c>
-      <c r="P26" s="18">
+      <c r="O26" s="4">
+        <v>1</v>
+      </c>
+      <c r="P26" s="4">
         <v>0.17</v>
       </c>
-      <c r="Q26" s="19">
+      <c r="Q26" s="5">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="R26" s="13"/>
+      <c r="R26" s="11"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="18">
+      <c r="A27" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="4">
         <v>0.749</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="4">
         <v>0.67700000000000005</v>
       </c>
-      <c r="D27" s="18">
-        <v>1</v>
-      </c>
-      <c r="E27" s="18">
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
         <v>0.77800000000000002</v>
       </c>
-      <c r="F27" s="11"/>
       <c r="G27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="J27" s="18">
-        <v>1</v>
-      </c>
-      <c r="K27" s="19">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11"/>
+      <c r="J27" s="4">
+        <v>1</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
       <c r="M27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="N27" s="19">
+      <c r="N27" s="5">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="O27" s="18">
+      <c r="O27" s="4">
         <v>0.17</v>
       </c>
-      <c r="P27" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="19">
-        <v>0</v>
-      </c>
-      <c r="R27" s="13"/>
+      <c r="P27" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>0</v>
+      </c>
+      <c r="R27" s="11"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="18">
+      <c r="A28" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="4">
         <v>0.67700000000000005</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="4">
         <v>0.67700000000000005</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="4">
         <v>0.77800000000000002</v>
       </c>
-      <c r="E28" s="18">
-        <v>1</v>
-      </c>
-      <c r="F28" s="11"/>
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
       <c r="G28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="J28" s="19">
-        <v>0</v>
-      </c>
-      <c r="K28" s="18">
-        <v>1</v>
-      </c>
-      <c r="L28" s="11"/>
+      <c r="J28" s="5">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
+        <v>1</v>
+      </c>
       <c r="M28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="4">
         <v>0.17</v>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="5">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="P28" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="18">
-        <v>1</v>
-      </c>
-      <c r="R28" s="13"/>
+      <c r="P28" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>1</v>
+      </c>
+      <c r="R28" s="11"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="16"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="13"/>
+      <c r="A29" s="13"/>
+      <c r="R29" s="11"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="16"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="13"/>
+      <c r="A30" s="13"/>
+      <c r="R30" s="11"/>
     </row>
     <row r="31" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="15" t="s">
+      <c r="M31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="13"/>
+      <c r="R31" s="11"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="12" t="s">
+      <c r="M32" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="13"/>
+      <c r="R32" s="11"/>
     </row>
     <row r="33" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="15" t="s">
+      <c r="M33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="13"/>
+      <c r="R33" s="11"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" s="16"/>
+      <c r="A34" s="13"/>
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1598,8 +1479,6 @@
       <c r="E34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
       <c r="H34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1612,8 +1491,6 @@
       <c r="K34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
       <c r="N34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1626,227 +1503,219 @@
       <c r="Q34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R34" s="13"/>
+      <c r="R34" s="11"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="18">
-        <v>1</v>
-      </c>
-      <c r="C35" s="18">
+      <c r="A35" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4">
         <v>0.3</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="4">
         <v>0.23799999999999999</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="4">
         <v>0.97799999999999998</v>
       </c>
-      <c r="F35" s="11"/>
       <c r="G35" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H35" s="18">
-        <v>1</v>
-      </c>
-      <c r="I35" s="18">
+      <c r="H35" s="4">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4">
         <v>0.23899999999999999</v>
       </c>
-      <c r="J35" s="18">
+      <c r="J35" s="4">
         <v>0.218</v>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="5">
         <v>2.4E-2</v>
       </c>
-      <c r="L35" s="11"/>
       <c r="M35" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N35" s="18">
-        <v>1</v>
-      </c>
-      <c r="O35" s="18">
+      <c r="N35" s="4">
+        <v>1</v>
+      </c>
+      <c r="O35" s="4">
         <v>0.68799999999999994</v>
       </c>
-      <c r="P35" s="18">
+      <c r="P35" s="4">
         <v>0.223</v>
       </c>
-      <c r="Q35" s="18">
+      <c r="Q35" s="4">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="R35" s="13"/>
+      <c r="R35" s="11"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="18">
+      <c r="A36" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4">
         <v>0.3</v>
       </c>
-      <c r="C36" s="18">
-        <v>1</v>
-      </c>
-      <c r="D36" s="18">
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36" s="4">
         <v>0.76300000000000001</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="4">
         <v>0.3</v>
       </c>
-      <c r="F36" s="11"/>
       <c r="G36" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="4">
         <v>0.23899999999999999</v>
       </c>
-      <c r="I36" s="18">
-        <v>1</v>
-      </c>
-      <c r="J36" s="19">
+      <c r="I36" s="4">
+        <v>1</v>
+      </c>
+      <c r="J36" s="5">
         <v>2.4E-2</v>
       </c>
-      <c r="K36" s="18">
+      <c r="K36" s="4">
         <v>0.218</v>
       </c>
-      <c r="L36" s="11"/>
       <c r="M36" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="N36" s="18">
+      <c r="N36" s="4">
         <v>0.68799999999999994</v>
       </c>
-      <c r="O36" s="18">
-        <v>1</v>
-      </c>
-      <c r="P36" s="18">
+      <c r="O36" s="4">
+        <v>1</v>
+      </c>
+      <c r="P36" s="4">
         <v>0.35599999999999998</v>
       </c>
-      <c r="Q36" s="19">
+      <c r="Q36" s="5">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="R36" s="13"/>
+      <c r="R36" s="11"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" s="18">
+      <c r="A37" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="4">
         <v>0.23799999999999999</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="4">
         <v>0.76300000000000001</v>
       </c>
-      <c r="D37" s="18">
-        <v>1</v>
-      </c>
-      <c r="E37" s="18">
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
         <v>0.23799999999999999</v>
       </c>
-      <c r="F37" s="11"/>
       <c r="G37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="4">
         <v>0.218</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="5">
         <v>2.4E-2</v>
       </c>
-      <c r="J37" s="18">
-        <v>1</v>
-      </c>
-      <c r="K37" s="19">
-        <v>0</v>
-      </c>
-      <c r="L37" s="11"/>
+      <c r="J37" s="4">
+        <v>1</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
       <c r="M37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="N37" s="18">
+      <c r="N37" s="4">
         <v>0.223</v>
       </c>
-      <c r="O37" s="18">
+      <c r="O37" s="4">
         <v>0.35599999999999998</v>
       </c>
-      <c r="P37" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="19">
+      <c r="P37" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="5">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="R37" s="13"/>
+      <c r="R37" s="11"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="18">
+      <c r="A38" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="4">
         <v>0.97799999999999998</v>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="4">
         <v>0.3</v>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="4">
         <v>0.23799999999999999</v>
       </c>
-      <c r="E38" s="18">
-        <v>1</v>
-      </c>
-      <c r="F38" s="11"/>
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="5">
         <v>2.4E-2</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="4">
         <v>0.218</v>
       </c>
-      <c r="J38" s="19">
-        <v>0</v>
-      </c>
-      <c r="K38" s="18">
-        <v>1</v>
-      </c>
-      <c r="L38" s="11"/>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4">
+        <v>1</v>
+      </c>
       <c r="M38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="18">
+      <c r="N38" s="4">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="O38" s="19">
+      <c r="O38" s="5">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="P38" s="19">
+      <c r="P38" s="5">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="Q38" s="18">
-        <v>1</v>
-      </c>
-      <c r="R38" s="13"/>
+      <c r="Q38" s="4">
+        <v>1</v>
+      </c>
+      <c r="R38" s="11"/>
     </row>
     <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="20"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21"/>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="21"/>
-      <c r="R39" s="22"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="16"/>
+      <c r="R39" s="17"/>
     </row>
     <row r="41" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">

--- a/Data/KW_dunn_results_withing_month.xlsx
+++ b/Data/KW_dunn_results_withing_month.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yaroslav\OneDrive\Рабочий стол\Python_repos\Python_projects_ICG_SB_RAS\Four_host_species_OF\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76438AB-565E-4583-A9F7-FCC85BEBA381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Liver_results" sheetId="1" r:id="rId1"/>
     <sheet name="Fluke_results" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="29">
   <si>
     <t>balb</t>
   </si>
@@ -47,18 +41,15 @@
     <t>Kruskal p-value for inflammation: 0.541</t>
   </si>
   <si>
-    <t>Kruskal p-value for PF: 0.575</t>
-  </si>
-  <si>
-    <t>Kruskal p-value for ChF: 0.178</t>
-  </si>
-  <si>
     <t>Kruskal p-value for AST: 0.010</t>
   </si>
   <si>
     <t>Kruskal p-value for ALT: 0.209</t>
   </si>
   <si>
+    <t>Kruskal p-value for Total_fibrosis: 0.178</t>
+  </si>
+  <si>
     <t>Group is 1_month</t>
   </si>
   <si>
@@ -68,18 +59,15 @@
     <t>Kruskal p-value for inflammation: 0.005</t>
   </si>
   <si>
-    <t>Kruskal p-value for PF: 0.001</t>
-  </si>
-  <si>
-    <t>Kruskal p-value for ChF: 0.001</t>
-  </si>
-  <si>
     <t>Kruskal p-value for AST: 0.001</t>
   </si>
   <si>
     <t>Kruskal p-value for ALT: 0.004</t>
   </si>
   <si>
+    <t>Kruskal p-value for Total_fibrosis: 0.005</t>
+  </si>
+  <si>
     <t>Group is 3_month</t>
   </si>
   <si>
@@ -89,10 +77,10 @@
     <t>Kruskal p-value for inflammation: 0.006</t>
   </si>
   <si>
-    <t>Kruskal p-value for ChF: 0.005</t>
-  </si>
-  <si>
     <t>Kruskal p-value for ALT: 0.007</t>
+  </si>
+  <si>
+    <t>Kruskal p-value for Total_fibrosis: 0.002</t>
   </si>
   <si>
     <t>Kruskal p-value for liver_flukes: 0.002</t>
@@ -119,8 +107,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,7 +156,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -191,106 +179,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -299,41 +192,19 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -371,7 +242,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -405,7 +276,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -440,10 +310,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -616,33 +485,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -653,7 +522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -691,7 +560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -702,7 +571,7 @@
         <v>0.06</v>
       </c>
       <c r="D5" s="4">
-        <v>0.59799999999999998</v>
+        <v>0.598</v>
       </c>
       <c r="E5" s="4">
         <v>0.85</v>
@@ -714,13 +583,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J5" s="4">
         <v>0.314</v>
       </c>
       <c r="K5" s="4">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>0</v>
@@ -729,16 +598,16 @@
         <v>1</v>
       </c>
       <c r="O5" s="4">
-        <v>0.70799999999999996</v>
+        <v>0.708</v>
       </c>
       <c r="P5" s="4">
         <v>0.372</v>
       </c>
       <c r="Q5" s="5">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -749,7 +618,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="E6" s="4">
         <v>0.06</v>
@@ -758,22 +627,22 @@
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
       </c>
       <c r="J6" s="4">
-        <v>0.25900000000000001</v>
+        <v>0.259</v>
       </c>
       <c r="K6" s="4">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.70799999999999996</v>
+        <v>0.708</v>
       </c>
       <c r="O6" s="4">
         <v>1</v>
@@ -782,24 +651,24 @@
         <v>0.247</v>
       </c>
       <c r="Q6" s="4">
-        <v>7.3999999999999996E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.074</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="4">
-        <v>0.59799999999999998</v>
+        <v>0.598</v>
       </c>
       <c r="C7" s="4">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>0.57899999999999996</v>
+        <v>0.579</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
@@ -808,13 +677,13 @@
         <v>0.314</v>
       </c>
       <c r="I7" s="4">
-        <v>0.25900000000000001</v>
+        <v>0.259</v>
       </c>
       <c r="J7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>2</v>
@@ -829,10 +698,10 @@
         <v>1</v>
       </c>
       <c r="Q7" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,7 +712,7 @@
         <v>0.06</v>
       </c>
       <c r="D8" s="4">
-        <v>0.57899999999999996</v>
+        <v>0.579</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -852,13 +721,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="I8" s="4">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="J8" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -867,41 +736,41 @@
         <v>3</v>
       </c>
       <c r="N8" s="5">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="O8" s="4">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="P8" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="Q8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -912,7 +781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17">
       <c r="B14" s="3" t="s">
         <v>0</v>
       </c>
@@ -950,7 +819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -958,13 +827,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="4">
-        <v>0.90900000000000003</v>
+        <v>0.909</v>
       </c>
       <c r="D15" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="E15" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>0</v>
@@ -973,13 +842,13 @@
         <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="J15" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="K15" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>0</v>
@@ -988,121 +857,121 @@
         <v>1</v>
       </c>
       <c r="O15" s="4">
-        <v>0.57399999999999995</v>
+        <v>0.574</v>
       </c>
       <c r="P15" s="4">
-        <v>0.32800000000000001</v>
+        <v>0.328</v>
       </c>
       <c r="Q15" s="4">
-        <v>5.6000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.056</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B16" s="4">
-        <v>0.90900000000000003</v>
+        <v>0.909</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="4">
-        <v>0.90900000000000003</v>
+        <v>0.909</v>
       </c>
       <c r="E16" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H16" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
       </c>
       <c r="J16" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="K16" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>0.57399999999999995</v>
+        <v>0.574</v>
       </c>
       <c r="O16" s="4">
         <v>1</v>
       </c>
       <c r="P16" s="4">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.14599999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="C17" s="4">
-        <v>0.90900000000000003</v>
+        <v>0.909</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="I17" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N17" s="4">
-        <v>0.32800000000000001</v>
+        <v>0.328</v>
       </c>
       <c r="O17" s="4">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="P17" s="4">
         <v>1</v>
       </c>
       <c r="Q17" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="C18" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="D18" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -1111,13 +980,13 @@
         <v>3</v>
       </c>
       <c r="H18" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="I18" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="J18" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
@@ -1126,59 +995,42 @@
         <v>3</v>
       </c>
       <c r="N18" s="4">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="O18" s="4">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="P18" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="Q18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:17">
+      <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="9"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="G21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R22" s="11"/>
-    </row>
-    <row r="23" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -1187,10 +1039,8 @@
       <c r="M23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R23" s="11"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+    </row>
+    <row r="24" spans="1:17">
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1227,23 +1077,22 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="11"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
       </c>
       <c r="C25" s="4">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0.749</v>
+        <v>0.788</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0.019</v>
       </c>
       <c r="E25" s="4">
-        <v>0.67700000000000005</v>
+        <v>0.285</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>0</v>
@@ -1252,13 +1101,13 @@
         <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>1</v>
+        <v>0.335</v>
       </c>
       <c r="J25" s="5">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="K25" s="5">
-        <v>5.3999999999999999E-2</v>
+        <v>0.017</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0.145</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>0</v>
@@ -1267,103 +1116,101 @@
         <v>1</v>
       </c>
       <c r="O25" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.349</v>
       </c>
       <c r="P25" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>0.037</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.17</v>
-      </c>
-      <c r="R25" s="11"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+        <v>0.171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>0.77800000000000002</v>
+        <v>0.788</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
-      <c r="D26" s="4">
-        <v>0.67700000000000005</v>
+      <c r="D26" s="5">
+        <v>0.016</v>
       </c>
       <c r="E26" s="4">
-        <v>0.67700000000000005</v>
+        <v>0.221</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H26" s="4">
-        <v>1</v>
+        <v>0.335</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
       </c>
       <c r="J26" s="5">
-        <v>5.3999999999999999E-2</v>
+        <v>0.001</v>
       </c>
       <c r="K26" s="5">
-        <v>5.3999999999999999E-2</v>
+        <v>0.017</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N26" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.349</v>
       </c>
       <c r="O26" s="4">
         <v>1</v>
       </c>
       <c r="P26" s="4">
-        <v>0.17</v>
+        <v>0.187</v>
       </c>
       <c r="Q26" s="5">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="R26" s="11"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="4">
-        <v>0.749</v>
-      </c>
-      <c r="C27" s="4">
-        <v>0.67700000000000005</v>
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0.019</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.016</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="4">
-        <v>0.77800000000000002</v>
+        <v>0.221</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H27" s="5">
-        <v>5.3999999999999999E-2</v>
+        <v>0.017</v>
       </c>
       <c r="I27" s="5">
-        <v>5.3999999999999999E-2</v>
+        <v>0.001</v>
       </c>
       <c r="J27" s="4">
         <v>1</v>
       </c>
-      <c r="K27" s="5">
-        <v>0</v>
+      <c r="K27" s="4">
+        <v>0.335</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N27" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>0.037</v>
       </c>
       <c r="O27" s="4">
-        <v>0.17</v>
+        <v>0.187</v>
       </c>
       <c r="P27" s="4">
         <v>1</v>
@@ -1371,20 +1218,19 @@
       <c r="Q27" s="5">
         <v>0</v>
       </c>
-      <c r="R27" s="11"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="14" t="s">
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="4">
-        <v>0.67700000000000005</v>
+        <v>0.285</v>
       </c>
       <c r="C28" s="4">
-        <v>0.67700000000000005</v>
+        <v>0.221</v>
       </c>
       <c r="D28" s="4">
-        <v>0.77800000000000002</v>
+        <v>0.221</v>
       </c>
       <c r="E28" s="4">
         <v>1</v>
@@ -1392,14 +1238,14 @@
       <c r="G28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H28" s="5">
-        <v>5.3999999999999999E-2</v>
+      <c r="H28" s="4">
+        <v>0.145</v>
       </c>
       <c r="I28" s="5">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J28" s="5">
-        <v>0</v>
+        <v>0.017</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0.335</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
@@ -1408,10 +1254,10 @@
         <v>3</v>
       </c>
       <c r="N28" s="4">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="O28" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>0.036</v>
       </c>
       <c r="P28" s="5">
         <v>0</v>
@@ -1419,42 +1265,31 @@
       <c r="Q28" s="4">
         <v>1</v>
       </c>
-      <c r="R28" s="11"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="R29" s="11"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="R30" s="11"/>
-    </row>
-    <row r="31" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R31" s="11"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="R32" s="11"/>
-    </row>
-    <row r="33" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -1463,10 +1298,8 @@
       <c r="M33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R33" s="11"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
+    </row>
+    <row r="34" spans="1:17">
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1503,23 +1336,22 @@
       <c r="Q34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R34" s="11"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" s="14" t="s">
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B35" s="4">
         <v>1</v>
       </c>
       <c r="C35" s="4">
-        <v>0.3</v>
+        <v>0.668</v>
       </c>
       <c r="D35" s="4">
-        <v>0.23799999999999999</v>
+        <v>0.341</v>
       </c>
       <c r="E35" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.668</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>0</v>
@@ -1528,13 +1360,13 @@
         <v>1</v>
       </c>
       <c r="I35" s="4">
-        <v>0.23899999999999999</v>
+        <v>0.274</v>
       </c>
       <c r="J35" s="4">
-        <v>0.218</v>
+        <v>0.19</v>
       </c>
       <c r="K35" s="5">
-        <v>2.4E-2</v>
+        <v>0.002</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>0</v>
@@ -1543,124 +1375,121 @@
         <v>1</v>
       </c>
       <c r="O35" s="4">
-        <v>0.68799999999999994</v>
+        <v>0.246</v>
       </c>
       <c r="P35" s="4">
-        <v>0.223</v>
-      </c>
-      <c r="Q35" s="4">
-        <v>7.9000000000000001E-2</v>
-      </c>
-      <c r="R35" s="11"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="14" t="s">
+        <v>0.392</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B36" s="4">
-        <v>0.3</v>
+        <v>0.668</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
       </c>
       <c r="D36" s="4">
-        <v>0.76300000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="E36" s="4">
-        <v>0.3</v>
+        <v>0.482</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H36" s="4">
-        <v>0.23899999999999999</v>
+        <v>0.274</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
       </c>
-      <c r="J36" s="5">
-        <v>2.4E-2</v>
-      </c>
-      <c r="K36" s="4">
-        <v>0.218</v>
+      <c r="J36" s="4">
+        <v>0.748</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0.051</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N36" s="4">
-        <v>0.68799999999999994</v>
+        <v>0.246</v>
       </c>
       <c r="O36" s="4">
         <v>1</v>
       </c>
-      <c r="P36" s="4">
-        <v>0.35599999999999998</v>
-      </c>
-      <c r="Q36" s="5">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="R36" s="11"/>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
+      <c r="P36" s="5">
+        <v>0.049</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>0.392</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="4">
-        <v>0.23799999999999999</v>
+        <v>0.341</v>
       </c>
       <c r="C37" s="4">
-        <v>0.76300000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" s="4">
-        <v>0.23799999999999999</v>
+        <v>0.482</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H37" s="4">
-        <v>0.218</v>
-      </c>
-      <c r="I37" s="5">
-        <v>2.4E-2</v>
+        <v>0.19</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0.748</v>
       </c>
       <c r="J37" s="4">
         <v>1</v>
       </c>
-      <c r="K37" s="5">
-        <v>0</v>
+      <c r="K37" s="4">
+        <v>0.078</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N37" s="4">
-        <v>0.223</v>
-      </c>
-      <c r="O37" s="4">
-        <v>0.35599999999999998</v>
+        <v>0.392</v>
+      </c>
+      <c r="O37" s="5">
+        <v>0.049</v>
       </c>
       <c r="P37" s="4">
         <v>1</v>
       </c>
       <c r="Q37" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="R37" s="11"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B38" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.668</v>
       </c>
       <c r="C38" s="4">
-        <v>0.3</v>
+        <v>0.482</v>
       </c>
       <c r="D38" s="4">
-        <v>0.23799999999999999</v>
+        <v>0.482</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -1669,13 +1498,13 @@
         <v>3</v>
       </c>
       <c r="H38" s="5">
-        <v>2.4E-2</v>
-      </c>
-      <c r="I38" s="4">
-        <v>0.218</v>
-      </c>
-      <c r="J38" s="5">
-        <v>0</v>
+        <v>0.002</v>
+      </c>
+      <c r="I38" s="5">
+        <v>0.051</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0.078</v>
       </c>
       <c r="K38" s="4">
         <v>1</v>
@@ -1683,63 +1512,42 @@
       <c r="M38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="4">
-        <v>7.9000000000000001E-2</v>
-      </c>
-      <c r="O38" s="5">
-        <v>4.1000000000000002E-2</v>
+      <c r="N38" s="5">
+        <v>0.049</v>
+      </c>
+      <c r="O38" s="4">
+        <v>0.392</v>
       </c>
       <c r="P38" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.008</v>
       </c>
       <c r="Q38" s="4">
         <v>1</v>
       </c>
-      <c r="R38" s="11"/>
-    </row>
-    <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="15"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="17"/>
-    </row>
-    <row r="41" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1750,7 +1558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17">
       <c r="B44" s="3" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17">
       <c r="A45" s="3" t="s">
         <v>0</v>
       </c>
@@ -1796,13 +1604,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="4">
-        <v>0.78800000000000003</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1.9E-2</v>
+        <v>0.3</v>
+      </c>
+      <c r="D45" s="4">
+        <v>0.238</v>
       </c>
       <c r="E45" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>0</v>
@@ -1811,13 +1619,13 @@
         <v>1</v>
       </c>
       <c r="I45" s="4">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="J45" s="5">
-        <v>1.7000000000000001E-2</v>
+        <v>0.915</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0.262</v>
       </c>
       <c r="K45" s="4">
-        <v>0.14499999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>0</v>
@@ -1826,121 +1634,121 @@
         <v>1</v>
       </c>
       <c r="O45" s="4">
-        <v>0.34899999999999998</v>
-      </c>
-      <c r="P45" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.239</v>
+      </c>
+      <c r="P45" s="4">
+        <v>0.108</v>
       </c>
       <c r="Q45" s="4">
-        <v>0.17100000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B46" s="4">
-        <v>0.78800000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="C46" s="4">
         <v>1</v>
       </c>
-      <c r="D46" s="5">
-        <v>1.6E-2</v>
+      <c r="D46" s="4">
+        <v>0.763</v>
       </c>
       <c r="E46" s="4">
-        <v>0.221</v>
+        <v>0.3</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H46" s="4">
-        <v>0.33500000000000002</v>
+        <v>0.915</v>
       </c>
       <c r="I46" s="4">
         <v>1</v>
       </c>
-      <c r="J46" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="K46" s="5">
-        <v>1.7000000000000001E-2</v>
+      <c r="J46" s="4">
+        <v>0.262</v>
+      </c>
+      <c r="K46" s="4">
+        <v>0.057</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N46" s="4">
-        <v>0.34899999999999998</v>
+        <v>0.239</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
       </c>
       <c r="P46" s="4">
-        <v>0.187</v>
+        <v>0.521</v>
       </c>
       <c r="Q46" s="5">
-        <v>3.5999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="5">
-        <v>1.9E-2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1.6E-2</v>
+      <c r="B47" s="4">
+        <v>0.238</v>
+      </c>
+      <c r="C47" s="4">
+        <v>0.763</v>
       </c>
       <c r="D47" s="4">
         <v>1</v>
       </c>
       <c r="E47" s="4">
-        <v>0.221</v>
+        <v>0.238</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H47" s="5">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="I47" s="5">
-        <v>1E-3</v>
+      <c r="H47" s="4">
+        <v>0.262</v>
+      </c>
+      <c r="I47" s="4">
+        <v>0.262</v>
       </c>
       <c r="J47" s="4">
         <v>1</v>
       </c>
-      <c r="K47" s="4">
-        <v>0.33500000000000002</v>
+      <c r="K47" s="5">
+        <v>0.003</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="N47" s="5">
-        <v>3.6999999999999998E-2</v>
+      <c r="N47" s="4">
+        <v>0.108</v>
       </c>
       <c r="O47" s="4">
-        <v>0.187</v>
+        <v>0.521</v>
       </c>
       <c r="P47" s="4">
         <v>1</v>
       </c>
       <c r="Q47" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B48" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="C48" s="4">
-        <v>0.221</v>
+        <v>0.3</v>
       </c>
       <c r="D48" s="4">
-        <v>0.221</v>
+        <v>0.238</v>
       </c>
       <c r="E48" s="4">
         <v>1</v>
@@ -1949,13 +1757,13 @@
         <v>3</v>
       </c>
       <c r="H48" s="4">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="I48" s="5">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="J48" s="4">
-        <v>0.33500000000000002</v>
+        <v>0.057</v>
+      </c>
+      <c r="I48" s="4">
+        <v>0.057</v>
+      </c>
+      <c r="J48" s="5">
+        <v>0.003</v>
       </c>
       <c r="K48" s="4">
         <v>1</v>
@@ -1964,274 +1772,15 @@
         <v>3</v>
       </c>
       <c r="N48" s="4">
-        <v>0.17100000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="O48" s="5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.012</v>
       </c>
       <c r="P48" s="5">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="Q48" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B54" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" s="4">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4">
-        <v>0.66800000000000004</v>
-      </c>
-      <c r="D55" s="4">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="E55" s="4">
-        <v>0.66800000000000004</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="H55" s="4">
-        <v>1</v>
-      </c>
-      <c r="I55" s="4">
-        <v>0.27400000000000002</v>
-      </c>
-      <c r="J55" s="4">
-        <v>0.19</v>
-      </c>
-      <c r="K55" s="5">
-        <v>2E-3</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="N55" s="4">
-        <v>1</v>
-      </c>
-      <c r="O55" s="4">
-        <v>0.246</v>
-      </c>
-      <c r="P55" s="4">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="Q55" s="5">
-        <v>4.9000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B56" s="4">
-        <v>0.66800000000000004</v>
-      </c>
-      <c r="C56" s="4">
-        <v>1</v>
-      </c>
-      <c r="D56" s="4">
-        <v>0.26600000000000001</v>
-      </c>
-      <c r="E56" s="4">
-        <v>0.48199999999999998</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="4">
-        <v>0.27400000000000002</v>
-      </c>
-      <c r="I56" s="4">
-        <v>1</v>
-      </c>
-      <c r="J56" s="4">
-        <v>0.748</v>
-      </c>
-      <c r="K56" s="5">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N56" s="4">
-        <v>0.246</v>
-      </c>
-      <c r="O56" s="4">
-        <v>1</v>
-      </c>
-      <c r="P56" s="5">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="Q56" s="4">
-        <v>0.39200000000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B57" s="4">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="C57" s="4">
-        <v>0.26600000000000001</v>
-      </c>
-      <c r="D57" s="4">
-        <v>1</v>
-      </c>
-      <c r="E57" s="4">
-        <v>0.48199999999999998</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H57" s="4">
-        <v>0.19</v>
-      </c>
-      <c r="I57" s="4">
-        <v>0.748</v>
-      </c>
-      <c r="J57" s="4">
-        <v>1</v>
-      </c>
-      <c r="K57" s="4">
-        <v>7.8E-2</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="N57" s="4">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="O57" s="5">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="P57" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="5">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B58" s="4">
-        <v>0.66800000000000004</v>
-      </c>
-      <c r="C58" s="4">
-        <v>0.48199999999999998</v>
-      </c>
-      <c r="D58" s="4">
-        <v>0.48199999999999998</v>
-      </c>
-      <c r="E58" s="4">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="5">
-        <v>2E-3</v>
-      </c>
-      <c r="I58" s="5">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="J58" s="4">
-        <v>7.8E-2</v>
-      </c>
-      <c r="K58" s="4">
-        <v>1</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="5">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="O58" s="4">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="P58" s="5">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Q58" s="4">
         <v>1</v>
       </c>
     </row>
@@ -2241,27 +1790,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2269,7 +1818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -2295,7 +1844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -2306,10 +1855,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="E5" s="4">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>0</v>
@@ -2321,13 +1870,13 @@
         <v>0.2</v>
       </c>
       <c r="J5" s="5">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="K5" s="4">
-        <v>0.26600000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -2338,10 +1887,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="E6" s="4">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>1</v>
@@ -2356,30 +1905,30 @@
         <v>0.2</v>
       </c>
       <c r="K6" s="5">
-        <v>2.1999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="C7" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="I7" s="4">
         <v>0.2</v>
@@ -2388,21 +1937,21 @@
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="4">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="C8" s="4">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="D8" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -2411,35 +1960,35 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>0.26600000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="I8" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="J8" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -2447,7 +1996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="B14" s="3" t="s">
         <v>0</v>
       </c>
@@ -2473,7 +2022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -2484,10 +2033,10 @@
         <v>0.95</v>
       </c>
       <c r="D15" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="E15" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>0</v>
@@ -2499,13 +2048,13 @@
         <v>0.214</v>
       </c>
       <c r="J15" s="4">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="K15" s="4">
         <v>0.15</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
@@ -2516,10 +2065,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="E16" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1</v>
@@ -2531,56 +2080,56 @@
         <v>1</v>
       </c>
       <c r="J16" s="4">
-        <v>0.64700000000000002</v>
+        <v>0.647</v>
       </c>
       <c r="K16" s="5">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="C17" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="4">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="I17" s="4">
-        <v>0.64700000000000002</v>
+        <v>0.647</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="C18" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="D18" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -2592,32 +2141,32 @@
         <v>0.15</v>
       </c>
       <c r="I18" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="J18" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -2625,7 +2174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -2651,7 +2200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
@@ -2659,10 +2208,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="4">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="D25" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
@@ -2674,36 +2223,36 @@
         <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="J25" s="5">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="K25" s="4">
-        <v>0.36199999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.362</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="E26" s="4">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H26" s="4">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
@@ -2712,30 +2261,30 @@
         <v>0.123</v>
       </c>
       <c r="K26" s="4">
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.094</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="C27" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H27" s="5">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="I27" s="4">
         <v>0.123</v>
@@ -2744,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="K27" s="5">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,10 +2304,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="4">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="D28" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="E28" s="4">
         <v>1</v>
@@ -2767,35 +2316,35 @@
         <v>3</v>
       </c>
       <c r="H28" s="4">
-        <v>0.36199999999999999</v>
+        <v>0.362</v>
       </c>
       <c r="I28" s="4">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="J28" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -2803,7 +2352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -2829,7 +2378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35" s="3" t="s">
         <v>0</v>
       </c>
@@ -2840,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="E35" s="4">
         <v>1</v>
@@ -2852,16 +2401,16 @@
         <v>1</v>
       </c>
       <c r="I35" s="4">
-        <v>0.81499999999999995</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J35" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="K35" s="4">
-        <v>0.53600000000000003</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.536</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="3" t="s">
         <v>1</v>
       </c>
@@ -2872,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
@@ -2881,51 +2430,51 @@
         <v>1</v>
       </c>
       <c r="H36" s="4">
-        <v>0.81499999999999995</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
       </c>
       <c r="J36" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="K36" s="4">
         <v>0.48</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="C37" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H37" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="I37" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="J37" s="4">
         <v>1</v>
       </c>
       <c r="K37" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
@@ -2936,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -2945,13 +2494,13 @@
         <v>3</v>
       </c>
       <c r="H38" s="4">
-        <v>0.53600000000000003</v>
+        <v>0.536</v>
       </c>
       <c r="I38" s="4">
         <v>0.48</v>
       </c>
       <c r="J38" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="K38" s="4">
         <v>1</v>

--- a/Data/KW_dunn_results_withing_month.xlsx
+++ b/Data/KW_dunn_results_withing_month.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e91640961c0a8f3d/Рабочий стол/Python_repos/Python_projects_ICG_SB_RAS/Four_host_species_OF/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_6364C174AEB0F24CC888A89E23012B66ADA97C07" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liver_results" sheetId="1" r:id="rId1"/>
     <sheet name="Fluke_results" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -107,8 +113,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,13 +204,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -242,7 +256,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -276,6 +290,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -310,9 +325,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -485,11 +501,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -500,7 +516,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -511,7 +527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -522,7 +538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -560,7 +576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -571,7 +587,7 @@
         <v>0.06</v>
       </c>
       <c r="D5" s="4">
-        <v>0.598</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="E5" s="4">
         <v>0.85</v>
@@ -583,13 +599,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="J5" s="4">
         <v>0.314</v>
       </c>
       <c r="K5" s="4">
-        <v>0.119</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>0</v>
@@ -598,16 +614,16 @@
         <v>1</v>
       </c>
       <c r="O5" s="4">
-        <v>0.708</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="P5" s="4">
         <v>0.372</v>
       </c>
       <c r="Q5" s="5">
-        <v>0.042</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>4.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -618,7 +634,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="E6" s="4">
         <v>0.06</v>
@@ -627,22 +643,22 @@
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
       </c>
       <c r="J6" s="4">
-        <v>0.259</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="K6" s="4">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.708</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="O6" s="4">
         <v>1</v>
@@ -651,24 +667,24 @@
         <v>0.247</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.074</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
+        <v>7.3999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="4">
-        <v>0.598</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="C7" s="4">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>0.579</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
@@ -677,13 +693,13 @@
         <v>0.314</v>
       </c>
       <c r="I7" s="4">
-        <v>0.259</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="J7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>0.008999999999999999</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>2</v>
@@ -698,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="Q7" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -712,7 +728,7 @@
         <v>0.06</v>
       </c>
       <c r="D8" s="4">
-        <v>0.579</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -721,13 +737,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>0.119</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="I8" s="4">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="J8" s="5">
-        <v>0.008999999999999999</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -736,19 +752,19 @@
         <v>3</v>
       </c>
       <c r="N8" s="5">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="O8" s="4">
-        <v>0.074</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="P8" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -759,7 +775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -770,7 +786,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -781,7 +797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>0</v>
       </c>
@@ -819,7 +835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -827,13 +843,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="4">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="D15" s="4">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="E15" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>0</v>
@@ -842,13 +858,13 @@
         <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="J15" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="K15" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>0</v>
@@ -857,121 +873,121 @@
         <v>1</v>
       </c>
       <c r="O15" s="4">
-        <v>0.574</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="P15" s="4">
-        <v>0.328</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.056</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B16" s="4">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="4">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="E16" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H16" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
       </c>
       <c r="J16" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="K16" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>0.574</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="O16" s="4">
         <v>1</v>
       </c>
       <c r="P16" s="4">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+        <v>0.14599999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="4">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="C17" s="4">
-        <v>0.909</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="I17" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N17" s="4">
-        <v>0.328</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="O17" s="4">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="P17" s="4">
         <v>1</v>
       </c>
       <c r="Q17" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="C18" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="D18" s="4">
-        <v>0.599</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -980,13 +996,13 @@
         <v>3</v>
       </c>
       <c r="H18" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I18" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="J18" s="5">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
@@ -995,19 +1011,19 @@
         <v>3</v>
       </c>
       <c r="N18" s="4">
-        <v>0.056</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="O18" s="4">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="P18" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -1018,7 +1034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
@@ -1029,7 +1045,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -1040,7 +1056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
@@ -1086,13 +1102,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="4">
-        <v>0.788</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="D25" s="5">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="E25" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>0</v>
@@ -1101,13 +1117,13 @@
         <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="J25" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="K25" s="4">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>0</v>
@@ -1116,27 +1132,27 @@
         <v>1</v>
       </c>
       <c r="O25" s="4">
-        <v>0.349</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="P25" s="5">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>0.788</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="5">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E26" s="4">
         <v>0.221</v>
@@ -1145,22 +1161,22 @@
         <v>1</v>
       </c>
       <c r="H26" s="4">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
       </c>
       <c r="J26" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="K26" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N26" s="4">
-        <v>0.349</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="O26" s="4">
         <v>1</v>
@@ -1169,18 +1185,18 @@
         <v>0.187</v>
       </c>
       <c r="Q26" s="5">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="5">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="C27" s="5">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
@@ -1192,22 +1208,22 @@
         <v>2</v>
       </c>
       <c r="H27" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="I27" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="J27" s="4">
         <v>1</v>
       </c>
       <c r="K27" s="4">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N27" s="5">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="O27" s="4">
         <v>0.187</v>
@@ -1219,12 +1235,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="4">
-        <v>0.285</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="C28" s="4">
         <v>0.221</v>
@@ -1239,13 +1255,13 @@
         <v>3</v>
       </c>
       <c r="H28" s="4">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="I28" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="J28" s="4">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
@@ -1254,10 +1270,10 @@
         <v>3</v>
       </c>
       <c r="N28" s="4">
-        <v>0.171</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="O28" s="5">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="P28" s="5">
         <v>0</v>
@@ -1266,7 +1282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -1288,7 +1304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -1299,7 +1315,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1337,7 +1353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>0</v>
       </c>
@@ -1345,13 +1361,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="4">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="D35" s="4">
-        <v>0.341</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="E35" s="4">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>0</v>
@@ -1360,13 +1376,13 @@
         <v>1</v>
       </c>
       <c r="I35" s="4">
-        <v>0.274</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="J35" s="4">
         <v>0.19</v>
       </c>
       <c r="K35" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>0</v>
@@ -1378,33 +1394,33 @@
         <v>0.246</v>
       </c>
       <c r="P35" s="4">
-        <v>0.392</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="Q35" s="5">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B36" s="4">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
       </c>
       <c r="D36" s="4">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H36" s="4">
-        <v>0.274</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
@@ -1413,7 +1429,7 @@
         <v>0.748</v>
       </c>
       <c r="K36" s="5">
-        <v>0.051</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>1</v>
@@ -1425,27 +1441,27 @@
         <v>1</v>
       </c>
       <c r="P36" s="5">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="Q36" s="4">
-        <v>0.392</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
+        <v>0.39200000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="4">
-        <v>0.341</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="C37" s="4">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" s="4">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>2</v>
@@ -1460,36 +1476,36 @@
         <v>1</v>
       </c>
       <c r="K37" s="4">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N37" s="4">
-        <v>0.392</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="O37" s="5">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="P37" s="4">
         <v>1</v>
       </c>
       <c r="Q37" s="5">
-        <v>0.008</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B38" s="4">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="C38" s="4">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="D38" s="4">
-        <v>0.482</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -1498,13 +1514,13 @@
         <v>3</v>
       </c>
       <c r="H38" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="I38" s="5">
-        <v>0.051</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="J38" s="4">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="K38" s="4">
         <v>1</v>
@@ -1513,19 +1529,19 @@
         <v>3</v>
       </c>
       <c r="N38" s="5">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="O38" s="4">
-        <v>0.392</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="P38" s="5">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="Q38" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
@@ -1536,7 +1552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -1547,7 +1563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1558,7 +1574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>0</v>
       </c>
@@ -1607,10 +1623,10 @@
         <v>0.3</v>
       </c>
       <c r="D45" s="4">
-        <v>0.238</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="E45" s="4">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>0</v>
@@ -1619,13 +1635,13 @@
         <v>1</v>
       </c>
       <c r="I45" s="4">
-        <v>0.915</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="J45" s="4">
-        <v>0.262</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="K45" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>0</v>
@@ -1634,16 +1650,16 @@
         <v>1</v>
       </c>
       <c r="O45" s="4">
-        <v>0.239</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="P45" s="4">
         <v>0.108</v>
       </c>
       <c r="Q45" s="4">
-        <v>0.163</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17">
+        <v>0.16300000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>1</v>
       </c>
@@ -1654,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="4">
-        <v>0.763</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="E46" s="4">
         <v>0.3</v>
@@ -1663,63 +1679,63 @@
         <v>1</v>
       </c>
       <c r="H46" s="4">
-        <v>0.915</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="I46" s="4">
         <v>1</v>
       </c>
       <c r="J46" s="4">
-        <v>0.262</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="K46" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N46" s="4">
-        <v>0.239</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
       </c>
       <c r="P46" s="4">
-        <v>0.521</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="Q46" s="5">
-        <v>0.012</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B47" s="4">
-        <v>0.238</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="C47" s="4">
-        <v>0.763</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="D47" s="4">
         <v>1</v>
       </c>
       <c r="E47" s="4">
-        <v>0.238</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H47" s="4">
-        <v>0.262</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="I47" s="4">
-        <v>0.262</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="J47" s="4">
         <v>1</v>
       </c>
       <c r="K47" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>2</v>
@@ -1728,27 +1744,27 @@
         <v>0.108</v>
       </c>
       <c r="O47" s="4">
-        <v>0.521</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="P47" s="4">
         <v>1</v>
       </c>
       <c r="Q47" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B48" s="4">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="C48" s="4">
         <v>0.3</v>
       </c>
       <c r="D48" s="4">
-        <v>0.238</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="E48" s="4">
         <v>1</v>
@@ -1757,13 +1773,13 @@
         <v>3</v>
       </c>
       <c r="H48" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I48" s="4">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="J48" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="K48" s="4">
         <v>1</v>
@@ -1772,13 +1788,13 @@
         <v>3</v>
       </c>
       <c r="N48" s="4">
-        <v>0.163</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="O48" s="5">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
       <c r="P48" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q48" s="4">
         <v>1</v>
@@ -1790,11 +1806,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1802,7 +1818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1810,7 +1826,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1818,7 +1834,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1844,7 +1860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -1855,10 +1871,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E5" s="4">
-        <v>0.765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>0</v>
@@ -1870,13 +1886,13 @@
         <v>0.2</v>
       </c>
       <c r="J5" s="5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="K5" s="4">
-        <v>0.266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>0.26600000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -1887,10 +1903,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E6" s="4">
-        <v>0.765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>1</v>
@@ -1905,30 +1921,30 @@
         <v>0.2</v>
       </c>
       <c r="K6" s="5">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="C7" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I7" s="4">
         <v>0.2</v>
@@ -1937,21 +1953,21 @@
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="4">
-        <v>0.765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="C8" s="4">
-        <v>0.765</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="D8" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -1960,19 +1976,19 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="I8" s="5">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="J8" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1980,7 +1996,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -1988,7 +2004,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -1996,7 +2012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>0</v>
       </c>
@@ -2022,7 +2038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -2033,10 +2049,10 @@
         <v>0.95</v>
       </c>
       <c r="D15" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E15" s="4">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>0</v>
@@ -2048,13 +2064,13 @@
         <v>0.214</v>
       </c>
       <c r="J15" s="4">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="K15" s="4">
         <v>0.15</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
@@ -2065,10 +2081,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E16" s="4">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1</v>
@@ -2080,56 +2096,56 @@
         <v>1</v>
       </c>
       <c r="J16" s="4">
-        <v>0.647</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="K16" s="5">
-        <v>0.008</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="C17" s="5">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="4">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="I17" s="4">
-        <v>0.647</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="C18" s="4">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="D18" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -2141,16 +2157,16 @@
         <v>0.15</v>
       </c>
       <c r="I18" s="5">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="J18" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
@@ -2158,7 +2174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -2166,7 +2182,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -2174,7 +2190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -2200,7 +2216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
@@ -2208,10 +2224,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="4">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="D25" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
@@ -2223,36 +2239,36 @@
         <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="J25" s="5">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="K25" s="4">
-        <v>0.362</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>0.36199999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="E26" s="4">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H26" s="4">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
@@ -2261,30 +2277,30 @@
         <v>0.123</v>
       </c>
       <c r="K26" s="4">
-        <v>0.094</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="C27" s="5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H27" s="5">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I27" s="4">
         <v>0.123</v>
@@ -2293,10 +2309,10 @@
         <v>1</v>
       </c>
       <c r="K27" s="5">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>3</v>
       </c>
@@ -2304,10 +2320,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="4">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="D28" s="5">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="E28" s="4">
         <v>1</v>
@@ -2316,19 +2332,19 @@
         <v>3</v>
       </c>
       <c r="H28" s="4">
-        <v>0.362</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="I28" s="4">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="J28" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>11</v>
       </c>
@@ -2336,7 +2352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>25</v>
       </c>
@@ -2344,7 +2360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -2352,7 +2368,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -2378,7 +2394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>0</v>
       </c>
@@ -2389,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="E35" s="4">
         <v>1</v>
@@ -2401,16 +2417,16 @@
         <v>1</v>
       </c>
       <c r="I35" s="4">
-        <v>0.8149999999999999</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="J35" s="5">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="K35" s="4">
-        <v>0.536</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>0.53600000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>1</v>
       </c>
@@ -2421,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
@@ -2430,51 +2446,51 @@
         <v>1</v>
       </c>
       <c r="H36" s="4">
-        <v>0.8149999999999999</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
       </c>
       <c r="J36" s="5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="K36" s="4">
         <v>0.48</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="C37" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H37" s="5">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="I37" s="5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="J37" s="4">
         <v>1</v>
       </c>
       <c r="K37" s="5">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
@@ -2485,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="5">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -2494,13 +2510,13 @@
         <v>3</v>
       </c>
       <c r="H38" s="4">
-        <v>0.536</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="I38" s="4">
         <v>0.48</v>
       </c>
       <c r="J38" s="5">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="K38" s="4">
         <v>1</v>

--- a/Data/KW_dunn_results_withing_month.xlsx
+++ b/Data/KW_dunn_results_withing_month.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e91640961c0a8f3d/Рабочий стол/Python_repos/Python_projects_ICG_SB_RAS/Four_host_species_OF/Data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6364C174AEB0F24CC888A89E23012B66ADA97C07" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Liver_results" sheetId="1" r:id="rId1"/>
     <sheet name="Fluke_results" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -38,7 +32,7 @@
     <t>Group is control</t>
   </si>
   <si>
-    <t>Kruskal p-value for hyperplasia: 0.049</t>
+    <t>Kruskal p-value for hyperplasia: 1.000</t>
   </si>
   <si>
     <t>Dunn's post-hoc values with FDR-BH:</t>
@@ -113,8 +107,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,21 +198,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -256,7 +242,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -290,7 +276,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -325,10 +310,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -501,11 +485,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -516,7 +500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -527,7 +511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -538,7 +522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -576,7 +560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -584,13 +568,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="4">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4">
-        <v>0.59799999999999998</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>0</v>
@@ -599,13 +583,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J5" s="4">
         <v>0.314</v>
       </c>
       <c r="K5" s="4">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>0</v>
@@ -614,51 +598,51 @@
         <v>1</v>
       </c>
       <c r="O5" s="4">
-        <v>0.70799999999999996</v>
+        <v>0.708</v>
       </c>
       <c r="P5" s="4">
         <v>0.372</v>
       </c>
       <c r="Q5" s="5">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="4">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>0.19700000000000001</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
       </c>
       <c r="J6" s="4">
-        <v>0.25900000000000001</v>
+        <v>0.259</v>
       </c>
       <c r="K6" s="4">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.70799999999999996</v>
+        <v>0.708</v>
       </c>
       <c r="O6" s="4">
         <v>1</v>
@@ -667,24 +651,24 @@
         <v>0.247</v>
       </c>
       <c r="Q6" s="4">
-        <v>7.3999999999999996E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.074</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="4">
-        <v>0.59799999999999998</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4">
-        <v>0.19700000000000001</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>0.57899999999999996</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
@@ -693,13 +677,13 @@
         <v>0.314</v>
       </c>
       <c r="I7" s="4">
-        <v>0.25900000000000001</v>
+        <v>0.259</v>
       </c>
       <c r="J7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>2</v>
@@ -714,21 +698,21 @@
         <v>1</v>
       </c>
       <c r="Q7" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="4">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="C8" s="4">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4">
-        <v>0.57899999999999996</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -737,13 +721,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="I8" s="4">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="J8" s="5">
-        <v>8.9999999999999993E-3</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -752,19 +736,19 @@
         <v>3</v>
       </c>
       <c r="N8" s="5">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="O8" s="4">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="P8" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="Q8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,7 +759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -786,7 +770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -797,7 +781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17">
       <c r="B14" s="3" t="s">
         <v>0</v>
       </c>
@@ -835,7 +819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -843,13 +827,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="4">
-        <v>0.90900000000000003</v>
+        <v>0.909</v>
       </c>
       <c r="D15" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="E15" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>0</v>
@@ -858,13 +842,13 @@
         <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="J15" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="K15" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>0</v>
@@ -873,121 +857,121 @@
         <v>1</v>
       </c>
       <c r="O15" s="4">
-        <v>0.57399999999999995</v>
+        <v>0.574</v>
       </c>
       <c r="P15" s="4">
-        <v>0.32800000000000001</v>
+        <v>0.328</v>
       </c>
       <c r="Q15" s="4">
-        <v>5.6000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.056</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B16" s="4">
-        <v>0.90900000000000003</v>
+        <v>0.909</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="4">
-        <v>0.90900000000000003</v>
+        <v>0.909</v>
       </c>
       <c r="E16" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H16" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
       </c>
       <c r="J16" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="K16" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>0.57399999999999995</v>
+        <v>0.574</v>
       </c>
       <c r="O16" s="4">
         <v>1</v>
       </c>
       <c r="P16" s="4">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.14599999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="C17" s="4">
-        <v>0.90900000000000003</v>
+        <v>0.909</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="I17" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N17" s="4">
-        <v>0.32800000000000001</v>
+        <v>0.328</v>
       </c>
       <c r="O17" s="4">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="P17" s="4">
         <v>1</v>
       </c>
       <c r="Q17" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="C18" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="D18" s="4">
-        <v>0.59899999999999998</v>
+        <v>0.599</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -996,13 +980,13 @@
         <v>3</v>
       </c>
       <c r="H18" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="I18" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="J18" s="5">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
@@ -1011,19 +995,19 @@
         <v>3</v>
       </c>
       <c r="N18" s="4">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="O18" s="4">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="P18" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="Q18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -1034,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17">
       <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
@@ -1045,7 +1029,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,7 +1040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17">
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -1094,7 +1078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17">
       <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
@@ -1102,13 +1086,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="4">
-        <v>0.78800000000000003</v>
+        <v>0.788</v>
       </c>
       <c r="D25" s="5">
-        <v>1.9E-2</v>
+        <v>0.019</v>
       </c>
       <c r="E25" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>0</v>
@@ -1117,13 +1101,13 @@
         <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>0.33500000000000002</v>
+        <v>0.335</v>
       </c>
       <c r="J25" s="5">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="K25" s="4">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>0</v>
@@ -1132,27 +1116,27 @@
         <v>1</v>
       </c>
       <c r="O25" s="4">
-        <v>0.34899999999999998</v>
+        <v>0.349</v>
       </c>
       <c r="P25" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="Q25" s="4">
-        <v>0.17100000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>0.78800000000000003</v>
+        <v>0.788</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="5">
-        <v>1.6E-2</v>
+        <v>0.016</v>
       </c>
       <c r="E26" s="4">
         <v>0.221</v>
@@ -1161,22 +1145,22 @@
         <v>1</v>
       </c>
       <c r="H26" s="4">
-        <v>0.33500000000000002</v>
+        <v>0.335</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
       </c>
       <c r="J26" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="K26" s="5">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N26" s="4">
-        <v>0.34899999999999998</v>
+        <v>0.349</v>
       </c>
       <c r="O26" s="4">
         <v>1</v>
@@ -1185,18 +1169,18 @@
         <v>0.187</v>
       </c>
       <c r="Q26" s="5">
-        <v>3.5999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="5">
-        <v>1.9E-2</v>
+        <v>0.019</v>
       </c>
       <c r="C27" s="5">
-        <v>1.6E-2</v>
+        <v>0.016</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
@@ -1208,22 +1192,22 @@
         <v>2</v>
       </c>
       <c r="H27" s="5">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="I27" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="J27" s="4">
         <v>1</v>
       </c>
       <c r="K27" s="4">
-        <v>0.33500000000000002</v>
+        <v>0.335</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N27" s="5">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="O27" s="4">
         <v>0.187</v>
@@ -1235,12 +1219,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17">
       <c r="A28" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.285</v>
       </c>
       <c r="C28" s="4">
         <v>0.221</v>
@@ -1255,13 +1239,13 @@
         <v>3</v>
       </c>
       <c r="H28" s="4">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="I28" s="5">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="J28" s="4">
-        <v>0.33500000000000002</v>
+        <v>0.335</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
@@ -1270,10 +1254,10 @@
         <v>3</v>
       </c>
       <c r="N28" s="4">
-        <v>0.17100000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="O28" s="5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="P28" s="5">
         <v>0</v>
@@ -1282,7 +1266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
@@ -1293,7 +1277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -1304,7 +1288,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -1315,7 +1299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17">
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1353,7 +1337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17">
       <c r="A35" s="3" t="s">
         <v>0</v>
       </c>
@@ -1361,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="4">
-        <v>0.66800000000000004</v>
+        <v>0.668</v>
       </c>
       <c r="D35" s="4">
-        <v>0.34100000000000003</v>
+        <v>0.341</v>
       </c>
       <c r="E35" s="4">
-        <v>0.66800000000000004</v>
+        <v>0.668</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>0</v>
@@ -1376,13 +1360,13 @@
         <v>1</v>
       </c>
       <c r="I35" s="4">
-        <v>0.27400000000000002</v>
+        <v>0.274</v>
       </c>
       <c r="J35" s="4">
         <v>0.19</v>
       </c>
       <c r="K35" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>0</v>
@@ -1394,33 +1378,33 @@
         <v>0.246</v>
       </c>
       <c r="P35" s="4">
-        <v>0.39200000000000002</v>
+        <v>0.392</v>
       </c>
       <c r="Q35" s="5">
-        <v>4.9000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B36" s="4">
-        <v>0.66800000000000004</v>
+        <v>0.668</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
       </c>
       <c r="D36" s="4">
-        <v>0.26600000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="E36" s="4">
-        <v>0.48199999999999998</v>
+        <v>0.482</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H36" s="4">
-        <v>0.27400000000000002</v>
+        <v>0.274</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
@@ -1429,7 +1413,7 @@
         <v>0.748</v>
       </c>
       <c r="K36" s="5">
-        <v>5.0999999999999997E-2</v>
+        <v>0.051</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>1</v>
@@ -1441,27 +1425,27 @@
         <v>1</v>
       </c>
       <c r="P36" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="Q36" s="4">
-        <v>0.39200000000000002</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.392</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="4">
-        <v>0.34100000000000003</v>
+        <v>0.341</v>
       </c>
       <c r="C37" s="4">
-        <v>0.26600000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" s="4">
-        <v>0.48199999999999998</v>
+        <v>0.482</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>2</v>
@@ -1476,36 +1460,36 @@
         <v>1</v>
       </c>
       <c r="K37" s="4">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="N37" s="4">
-        <v>0.39200000000000002</v>
+        <v>0.392</v>
       </c>
       <c r="O37" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="P37" s="4">
         <v>1</v>
       </c>
       <c r="Q37" s="5">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B38" s="4">
-        <v>0.66800000000000004</v>
+        <v>0.668</v>
       </c>
       <c r="C38" s="4">
-        <v>0.48199999999999998</v>
+        <v>0.482</v>
       </c>
       <c r="D38" s="4">
-        <v>0.48199999999999998</v>
+        <v>0.482</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -1514,13 +1498,13 @@
         <v>3</v>
       </c>
       <c r="H38" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="I38" s="5">
-        <v>5.0999999999999997E-2</v>
+        <v>0.051</v>
       </c>
       <c r="J38" s="4">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="K38" s="4">
         <v>1</v>
@@ -1529,19 +1513,19 @@
         <v>3</v>
       </c>
       <c r="N38" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="O38" s="4">
-        <v>0.39200000000000002</v>
+        <v>0.392</v>
       </c>
       <c r="P38" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="Q38" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
@@ -1552,7 +1536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -1563,7 +1547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1574,7 +1558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17">
       <c r="B44" s="3" t="s">
         <v>0</v>
       </c>
@@ -1612,7 +1596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17">
       <c r="A45" s="3" t="s">
         <v>0</v>
       </c>
@@ -1623,10 +1607,10 @@
         <v>0.3</v>
       </c>
       <c r="D45" s="4">
-        <v>0.23799999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="E45" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>0</v>
@@ -1635,13 +1619,13 @@
         <v>1</v>
       </c>
       <c r="I45" s="4">
-        <v>0.91500000000000004</v>
+        <v>0.915</v>
       </c>
       <c r="J45" s="4">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="K45" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>0</v>
@@ -1650,16 +1634,16 @@
         <v>1</v>
       </c>
       <c r="O45" s="4">
-        <v>0.23899999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="P45" s="4">
         <v>0.108</v>
       </c>
       <c r="Q45" s="4">
-        <v>0.16300000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="3" t="s">
         <v>1</v>
       </c>
@@ -1670,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="4">
-        <v>0.76300000000000001</v>
+        <v>0.763</v>
       </c>
       <c r="E46" s="4">
         <v>0.3</v>
@@ -1679,63 +1663,63 @@
         <v>1</v>
       </c>
       <c r="H46" s="4">
-        <v>0.91500000000000004</v>
+        <v>0.915</v>
       </c>
       <c r="I46" s="4">
         <v>1</v>
       </c>
       <c r="J46" s="4">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="K46" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="N46" s="4">
-        <v>0.23899999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
       </c>
       <c r="P46" s="4">
-        <v>0.52100000000000002</v>
+        <v>0.521</v>
       </c>
       <c r="Q46" s="5">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B47" s="4">
-        <v>0.23799999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="C47" s="4">
-        <v>0.76300000000000001</v>
+        <v>0.763</v>
       </c>
       <c r="D47" s="4">
         <v>1</v>
       </c>
       <c r="E47" s="4">
-        <v>0.23799999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H47" s="4">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="I47" s="4">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="J47" s="4">
         <v>1</v>
       </c>
       <c r="K47" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>2</v>
@@ -1744,27 +1728,27 @@
         <v>0.108</v>
       </c>
       <c r="O47" s="4">
-        <v>0.52100000000000002</v>
+        <v>0.521</v>
       </c>
       <c r="P47" s="4">
         <v>1</v>
       </c>
       <c r="Q47" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B48" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="C48" s="4">
         <v>0.3</v>
       </c>
       <c r="D48" s="4">
-        <v>0.23799999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="E48" s="4">
         <v>1</v>
@@ -1773,13 +1757,13 @@
         <v>3</v>
       </c>
       <c r="H48" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="I48" s="4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="J48" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="K48" s="4">
         <v>1</v>
@@ -1788,13 +1772,13 @@
         <v>3</v>
       </c>
       <c r="N48" s="4">
-        <v>0.16300000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="O48" s="5">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="P48" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="Q48" s="4">
         <v>1</v>
@@ -1806,11 +1790,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1818,7 +1802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1826,7 +1810,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1834,7 +1818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1860,7 +1844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -1871,10 +1855,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="E5" s="4">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>0</v>
@@ -1886,13 +1870,13 @@
         <v>0.2</v>
       </c>
       <c r="J5" s="5">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="K5" s="4">
-        <v>0.26600000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -1903,10 +1887,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="E6" s="4">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>1</v>
@@ -1921,30 +1905,30 @@
         <v>0.2</v>
       </c>
       <c r="K6" s="5">
-        <v>2.1999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="C7" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="I7" s="4">
         <v>0.2</v>
@@ -1953,21 +1937,21 @@
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="4">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="C8" s="4">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="D8" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -1976,19 +1960,19 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>0.26600000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="I8" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="J8" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1996,7 +1980,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -2004,7 +1988,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -2012,7 +1996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="B14" s="3" t="s">
         <v>0</v>
       </c>
@@ -2038,7 +2022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -2049,10 +2033,10 @@
         <v>0.95</v>
       </c>
       <c r="D15" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="E15" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>0</v>
@@ -2064,13 +2048,13 @@
         <v>0.214</v>
       </c>
       <c r="J15" s="4">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="K15" s="4">
         <v>0.15</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
@@ -2081,10 +2065,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="E16" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1</v>
@@ -2096,56 +2080,56 @@
         <v>1</v>
       </c>
       <c r="J16" s="4">
-        <v>0.64700000000000002</v>
+        <v>0.647</v>
       </c>
       <c r="K16" s="5">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="C17" s="5">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="4">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="I17" s="4">
-        <v>0.64700000000000002</v>
+        <v>0.647</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="C18" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="D18" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -2157,16 +2141,16 @@
         <v>0.15</v>
       </c>
       <c r="I18" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="J18" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
@@ -2174,7 +2158,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -2182,7 +2166,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -2190,7 +2174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
@@ -2216,7 +2200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
@@ -2224,10 +2208,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="4">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="D25" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
@@ -2239,36 +2223,36 @@
         <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="J25" s="5">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="K25" s="4">
-        <v>0.36199999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.362</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B26" s="4">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="E26" s="4">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H26" s="4">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
@@ -2277,30 +2261,30 @@
         <v>0.123</v>
       </c>
       <c r="K26" s="4">
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.094</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="C27" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H27" s="5">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="I27" s="4">
         <v>0.123</v>
@@ -2309,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="K27" s="5">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,10 +2304,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="4">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="D28" s="5">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="E28" s="4">
         <v>1</v>
@@ -2332,19 +2316,19 @@
         <v>3</v>
       </c>
       <c r="H28" s="4">
-        <v>0.36199999999999999</v>
+        <v>0.362</v>
       </c>
       <c r="I28" s="4">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="J28" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
         <v>11</v>
       </c>
@@ -2352,7 +2336,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11">
       <c r="A32" s="2" t="s">
         <v>25</v>
       </c>
@@ -2360,7 +2344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -2368,7 +2352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
@@ -2394,7 +2378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35" s="3" t="s">
         <v>0</v>
       </c>
@@ -2405,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="E35" s="4">
         <v>1</v>
@@ -2417,16 +2401,16 @@
         <v>1</v>
       </c>
       <c r="I35" s="4">
-        <v>0.81499999999999995</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J35" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="K35" s="4">
-        <v>0.53600000000000003</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.536</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="3" t="s">
         <v>1</v>
       </c>
@@ -2437,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
@@ -2446,51 +2430,51 @@
         <v>1</v>
       </c>
       <c r="H36" s="4">
-        <v>0.81499999999999995</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
       </c>
       <c r="J36" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="K36" s="4">
         <v>0.48</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="C37" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H37" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="I37" s="5">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="J37" s="4">
         <v>1</v>
       </c>
       <c r="K37" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="3" t="s">
         <v>3</v>
       </c>
@@ -2501,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -2510,13 +2494,13 @@
         <v>3</v>
       </c>
       <c r="H38" s="4">
-        <v>0.53600000000000003</v>
+        <v>0.536</v>
       </c>
       <c r="I38" s="4">
         <v>0.48</v>
       </c>
       <c r="J38" s="5">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="K38" s="4">
         <v>1</v>
